--- a/بنيان/الموردين/المورد.xlsx
+++ b/بنيان/الموردين/المورد.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\بنيان\الموردين\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mo'men Khalid\work\بنيان\الموردين\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF81E0D-A2A6-4D4A-9A11-041C200C0F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDF4FEF-20A2-4D68-BE33-99E94B121581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المورد" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>هوية شخصية</t>
   </si>
@@ -599,13 +599,22 @@
   </si>
   <si>
     <t>DIVERSE-2026-90001</t>
+  </si>
+  <si>
+    <t>شركه ريال مان</t>
+  </si>
+  <si>
+    <t>ELECT-2026-30014</t>
+  </si>
+  <si>
+    <t>01224623096</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,8 +635,14 @@
       <color rgb="FF1F1F1F"/>
       <name val="Inherit"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,8 +655,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -649,11 +676,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -665,6 +707,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -1362,7 +1408,7 @@
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="2:5">
+    <row r="33" spans="1:17">
       <c r="B33" t="s">
         <v>30</v>
       </c>
@@ -1374,7 +1420,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="2:5">
+    <row r="34" spans="1:17">
       <c r="B34" t="s">
         <v>31</v>
       </c>
@@ -1386,7 +1432,7 @@
       </c>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="2:5">
+    <row r="35" spans="1:17">
       <c r="B35" t="s">
         <v>32</v>
       </c>
@@ -1400,7 +1446,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="36" spans="2:5">
+    <row r="36" spans="1:17">
       <c r="B36" t="s">
         <v>36</v>
       </c>
@@ -1412,7 +1458,7 @@
       </c>
       <c r="E36" s="3"/>
     </row>
-    <row r="37" spans="2:5">
+    <row r="37" spans="1:17">
       <c r="B37" t="s">
         <v>21</v>
       </c>
@@ -1424,7 +1470,7 @@
       </c>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="2:5">
+    <row r="38" spans="1:17">
       <c r="B38" t="s">
         <v>109</v>
       </c>
@@ -1436,7 +1482,7 @@
       </c>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="2:5">
+    <row r="39" spans="1:17">
       <c r="B39" t="s">
         <v>110</v>
       </c>
@@ -1448,7 +1494,7 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="2:5">
+    <row r="40" spans="1:17">
       <c r="B40" t="s">
         <v>16</v>
       </c>
@@ -1460,7 +1506,7 @@
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="2:5">
+    <row r="41" spans="1:17">
       <c r="B41" t="s">
         <v>26</v>
       </c>
@@ -1472,7 +1518,7 @@
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="2:5">
+    <row r="42" spans="1:17">
       <c r="B42" t="s">
         <v>27</v>
       </c>
@@ -1484,7 +1530,7 @@
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="2:5">
+    <row r="43" spans="1:17">
       <c r="B43" t="s">
         <v>123</v>
       </c>
@@ -1496,7 +1542,7 @@
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="2:5">
+    <row r="44" spans="1:17">
       <c r="B44" t="s">
         <v>37</v>
       </c>
@@ -1508,7 +1554,7 @@
       </c>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="2:5">
+    <row r="45" spans="1:17">
       <c r="B45" t="s">
         <v>19</v>
       </c>
@@ -1520,272 +1566,298 @@
       </c>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="2:5" s="4" customFormat="1">
-      <c r="B46" s="4" t="s">
+    <row r="46" spans="1:17" s="8" customFormat="1">
+      <c r="A46" s="7"/>
+      <c r="B46" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+    </row>
+    <row r="47" spans="1:17" s="4" customFormat="1">
+      <c r="B47" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" t="s">
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="B48" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="48" spans="2:5">
-      <c r="B48" t="s">
-        <v>39</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" t="s">
         <v>20</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="2:5" s="4" customFormat="1">
-      <c r="B50" s="4" t="s">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="2:5" s="4" customFormat="1">
+      <c r="B51" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="2:5">
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="3"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="2:5">
+      <c r="B53" t="s">
         <v>107</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="2:5" s="4" customFormat="1">
-      <c r="B53" s="4" t="s">
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="2:5" s="4" customFormat="1">
+      <c r="B54" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-    </row>
-    <row r="54" spans="2:5">
-      <c r="B54" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" s="3"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E55" s="3"/>
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C57" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="2:5" s="4" customFormat="1">
-      <c r="B57" s="4" t="s">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="2:5" s="4" customFormat="1">
+      <c r="B58" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="2:5">
-      <c r="B58" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" t="s">
-        <v>183</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="3"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="C59" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="3">
-        <v>1117551822</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>115</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" s="3">
+        <v>1117551822</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" t="s">
         <v>104</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>185</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D61" s="3">
         <v>1128832397</v>
       </c>
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="2:5" s="4" customFormat="1">
-      <c r="B61" s="4" t="s">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="2:5" s="4" customFormat="1">
+      <c r="B62" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="3">
-        <v>1030940663</v>
-      </c>
-      <c r="E62" s="3"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>51</v>
+        <v>186</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1030940663</v>
       </c>
       <c r="E63" s="3"/>
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E64" s="3"/>
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="E65" s="3"/>
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E66" s="3"/>
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" t="s">
         <v>112</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>191</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="2:5" s="4" customFormat="1">
-      <c r="B68" s="4" t="s">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="2:5" s="4" customFormat="1">
+      <c r="B69" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="69" spans="2:5">
-      <c r="B69" t="s">
+    <row r="70" spans="2:5">
+      <c r="B70" t="s">
         <v>34</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>192</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="2:5" s="4" customFormat="1">
-      <c r="B70" s="4" t="s">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="2:5" s="4" customFormat="1">
+      <c r="B71" s="4" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>